--- a/data/Class.xlsx
+++ b/data/Class.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,41 @@
           <t>skill</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>init_health</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>init_mana</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>init_strength</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>init_armor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>init_resistance</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>init_critchance</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>init_speed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +474,41 @@
           <t>repeated uint32</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>uint64</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,9 +521,42 @@
           <t>common</t>
         </is>
       </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>
@@ -466,6 +569,27 @@
       </c>
       <c r="D6" t="n">
         <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>200</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -481,6 +605,27 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
+      <c r="E7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -495,6 +640,27 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
+      <c r="E8" t="n">
+        <v>500</v>
+      </c>
+      <c r="F8" t="n">
+        <v>200</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -509,6 +675,27 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -522,6 +709,27 @@
       </c>
       <c r="D10" t="n">
         <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>200</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -537,6 +745,27 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -551,6 +780,27 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="n">
+        <v>500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +815,27 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="n">
+        <v>500</v>
+      </c>
+      <c r="F13" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -578,6 +849,27 @@
       </c>
       <c r="D14" t="n">
         <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>500</v>
+      </c>
+      <c r="F14" t="n">
+        <v>200</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/Class.xlsx
+++ b/data/Class.xlsx
@@ -428,30 +428,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>repeated uint32</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4"/>
     <row r="5"/>
     <row r="6">
